--- a/astro-site/public/dl/kit-tareas-heladeria/05-tareas-semanales-mensuales.xlsx
+++ b/astro-site/public/dl/kit-tareas-heladeria/05-tareas-semanales-mensuales.xlsx
@@ -932,7 +932,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Desmontar y limpiar piezas de mantecadora (cuchillas, junta, cilindro)</t>
+          <t>Desmontar y limpiar piezas de mantecadora (cuchillas, batidor y junta; el cilindro, en su sitio)</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Test de mantecadora en vacío: verificar temperatura y ciclo</t>
+          <t>Revisar la mantecadora según el fabricante: cuchillas, batidor y junta; temperatura de extracción en la primera tanda (nunca en vacío)</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
